--- a/data/gravel/Singular Peregrine 2025.xlsx
+++ b/data/gravel/Singular Peregrine 2025.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10810"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10824"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C3E59998-A16D-3143-9244-4CFE5F07AC90}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C3452D7C-A8A2-D642-B79F-FBDEBE91E8F0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="2900" yWindow="2780" windowWidth="25900" windowHeight="14700" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -353,9 +353,6 @@
     <t>Singular</t>
   </si>
   <si>
-    <t>Peregrine</t>
-  </si>
-  <si>
     <t>seat_tube_ct</t>
   </si>
   <si>
@@ -369,6 +366,9 @@
   </si>
   <si>
     <t>a8:f35</t>
+  </si>
+  <si>
+    <t>Peregrine MK4</t>
   </si>
 </sst>
 </file>
@@ -779,7 +779,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
     </row>
     <row r="3" spans="1:22" x14ac:dyDescent="0.3">
@@ -811,7 +811,7 @@
         <v>5</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="8" spans="1:22" ht="22" x14ac:dyDescent="0.3">
@@ -954,7 +954,7 @@
     </row>
     <row r="12" spans="1:22" ht="22" x14ac:dyDescent="0.3">
       <c r="A12" s="2" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B12" s="9" t="s">
         <v>87</v>
@@ -1758,7 +1758,7 @@
         <v>49</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.3">
@@ -1800,7 +1800,7 @@
         <v>55</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.3">
@@ -1866,7 +1866,7 @@
         <v>67</v>
       </c>
       <c r="B75" s="2" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
   </sheetData>

--- a/data/gravel/Singular Peregrine 2025.xlsx
+++ b/data/gravel/Singular Peregrine 2025.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10824"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11003"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C3452D7C-A8A2-D642-B79F-FBDEBE91E8F0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2B30B3B9-552C-3F44-844B-34D876A35C9D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2900" yWindow="2780" windowWidth="25900" windowHeight="14700" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="33840" yWindow="-22960" windowWidth="25900" windowHeight="14700" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="112">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="113">
   <si>
     <t>brand</t>
   </si>
@@ -369,6 +369,9 @@
   </si>
   <si>
     <t>Peregrine MK4</t>
+  </si>
+  <si>
+    <t>https://singularcycles.com/cdn/shop/files/3-IMG_6116.webp?v=1749219848&amp;width=750</t>
   </si>
 </sst>
 </file>
@@ -806,6 +809,11 @@
         <v>104</v>
       </c>
     </row>
+    <row r="6" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="B6" s="2" t="s">
+        <v>112</v>
+      </c>
+    </row>
     <row r="7" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
         <v>5</v>

--- a/data/gravel/Singular Peregrine 2025.xlsx
+++ b/data/gravel/Singular Peregrine 2025.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11003"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11012"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2B30B3B9-552C-3F44-844B-34D876A35C9D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F1FA8161-BBB7-D141-B92D-7B181CDB6545}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="33840" yWindow="-22960" windowWidth="25900" windowHeight="14700" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="113">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="119" uniqueCount="115">
   <si>
     <t>brand</t>
   </si>
@@ -362,9 +362,6 @@
     <t>internal</t>
   </si>
   <si>
-    <t>usd</t>
-  </si>
-  <si>
     <t>a8:f35</t>
   </si>
   <si>
@@ -372,6 +369,15 @@
   </si>
   <si>
     <t>https://singularcycles.com/cdn/shop/files/3-IMG_6116.webp?v=1749219848&amp;width=750</t>
+  </si>
+  <si>
+    <t>location</t>
+  </si>
+  <si>
+    <t>Watford, Hertfordshire, England</t>
+  </si>
+  <si>
+    <t>USD</t>
   </si>
 </sst>
 </file>
@@ -760,7 +766,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:V75"/>
+  <dimension ref="A1:V76"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="20" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="19.6640625" style="2" customWidth="1"/>
@@ -782,7 +788,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="3" spans="1:22" x14ac:dyDescent="0.3">
@@ -811,7 +817,7 @@
     </row>
     <row r="6" spans="1:22" x14ac:dyDescent="0.3">
       <c r="B6" s="2" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="7" spans="1:22" x14ac:dyDescent="0.3">
@@ -819,7 +825,7 @@
         <v>5</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="8" spans="1:22" ht="22" x14ac:dyDescent="0.3">
@@ -1874,7 +1880,15 @@
         <v>67</v>
       </c>
       <c r="B75" s="2" t="s">
-        <v>109</v>
+        <v>114</v>
+      </c>
+    </row>
+    <row r="76" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A76" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="B76" s="2" t="s">
+        <v>113</v>
       </c>
     </row>
   </sheetData>

--- a/data/gravel/Singular Peregrine 2025.xlsx
+++ b/data/gravel/Singular Peregrine 2025.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11012"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11018"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F1FA8161-BBB7-D141-B92D-7B181CDB6545}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3AD870D0-533E-2641-BD13-7CD00CD266E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="119" uniqueCount="115">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="113">
   <si>
     <t>brand</t>
   </si>
@@ -263,12 +263,6 @@
     <t>threaded</t>
   </si>
   <si>
-    <t>rider_min_spec</t>
-  </si>
-  <si>
-    <t>rider_max_spec</t>
-  </si>
-  <si>
     <t>Wheelbase</t>
   </si>
   <si>
@@ -362,9 +356,6 @@
     <t>internal</t>
   </si>
   <si>
-    <t>a8:f35</t>
-  </si>
-  <si>
     <t>Peregrine MK4</t>
   </si>
   <si>
@@ -378,6 +369,9 @@
   </si>
   <si>
     <t>USD</t>
+  </si>
+  <si>
+    <t>a8:f33</t>
   </si>
 </sst>
 </file>
@@ -766,7 +760,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:V76"/>
+  <dimension ref="A1:V74"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="20" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="19.6640625" style="2" customWidth="1"/>
@@ -780,7 +774,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
     </row>
     <row r="2" spans="1:22" x14ac:dyDescent="0.3">
@@ -788,7 +782,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
     </row>
     <row r="3" spans="1:22" x14ac:dyDescent="0.3">
@@ -812,12 +806,12 @@
         <v>4</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
     </row>
     <row r="6" spans="1:22" x14ac:dyDescent="0.3">
       <c r="B6" s="2" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
     </row>
     <row r="7" spans="1:22" x14ac:dyDescent="0.3">
@@ -825,7 +819,7 @@
         <v>5</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
     </row>
     <row r="8" spans="1:22" ht="22" x14ac:dyDescent="0.3">
@@ -833,19 +827,19 @@
         <v>6</v>
       </c>
       <c r="B8" s="9" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="C8" s="9" t="s">
+        <v>98</v>
+      </c>
+      <c r="D8" s="7" t="s">
+        <v>99</v>
+      </c>
+      <c r="E8" s="7" t="s">
         <v>100</v>
       </c>
-      <c r="D8" s="7" t="s">
+      <c r="F8" s="7" t="s">
         <v>101</v>
-      </c>
-      <c r="E8" s="7" t="s">
-        <v>102</v>
-      </c>
-      <c r="F8" s="7" t="s">
-        <v>103</v>
       </c>
       <c r="G8" s="7"/>
       <c r="H8" s="7"/>
@@ -869,7 +863,7 @@
         <v>17</v>
       </c>
       <c r="B9" s="9" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="C9" s="10">
         <v>362</v>
@@ -903,7 +897,7 @@
         <v>16</v>
       </c>
       <c r="B10" s="9" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="C10" s="10">
         <v>556</v>
@@ -937,7 +931,7 @@
         <v>7</v>
       </c>
       <c r="B11" s="9" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="C11" s="10">
         <v>520</v>
@@ -968,10 +962,10 @@
     </row>
     <row r="12" spans="1:22" ht="22" x14ac:dyDescent="0.3">
       <c r="A12" s="2" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="B12" s="9" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="C12" s="10">
         <v>537</v>
@@ -1005,7 +999,7 @@
         <v>9</v>
       </c>
       <c r="B13" s="9" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="C13" s="10">
         <v>515</v>
@@ -1039,7 +1033,7 @@
         <v>11</v>
       </c>
       <c r="B14" s="9" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="C14" s="10">
         <v>71</v>
@@ -1073,7 +1067,7 @@
         <v>8</v>
       </c>
       <c r="B15" s="9" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="C15" s="10">
         <v>74</v>
@@ -1107,7 +1101,7 @@
         <v>10</v>
       </c>
       <c r="B16" s="9" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="C16" s="10">
         <v>110</v>
@@ -1141,7 +1135,7 @@
         <v>14</v>
       </c>
       <c r="B17" s="9" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="C17" s="10">
         <v>445</v>
@@ -1176,7 +1170,7 @@
         <v>19</v>
       </c>
       <c r="B18" s="9" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="C18" s="10">
         <v>1021</v>
@@ -1208,10 +1202,10 @@
     </row>
     <row r="19" spans="1:21" ht="22" x14ac:dyDescent="0.3">
       <c r="A19" s="2" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="B19" s="9" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="C19" s="10">
         <v>591</v>
@@ -1245,7 +1239,7 @@
         <v>18</v>
       </c>
       <c r="B20" s="9" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="C20" s="10">
         <v>822</v>
@@ -1276,10 +1270,10 @@
     </row>
     <row r="21" spans="1:21" ht="22" x14ac:dyDescent="0.3">
       <c r="A21" s="2" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="B21" s="9" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="C21" s="10">
         <v>69</v>
@@ -1536,19 +1530,15 @@
         <v>28</v>
       </c>
       <c r="C32" s="2">
-        <f>C34</f>
         <v>160</v>
       </c>
       <c r="D32" s="2">
-        <f>AVERAGE(D34,C35)</f>
         <v>168</v>
       </c>
       <c r="E32" s="2">
-        <f t="shared" ref="E32:F32" si="0">AVERAGE(E34,D35)</f>
-        <v>176.5</v>
+        <v>178</v>
       </c>
       <c r="F32" s="2">
-        <f t="shared" si="0"/>
         <v>186</v>
       </c>
     </row>
@@ -1560,335 +1550,297 @@
         <v>30</v>
       </c>
       <c r="C33" s="2">
-        <f>D32</f>
         <v>168</v>
       </c>
       <c r="D33" s="2">
-        <f t="shared" ref="D33:F33" si="1">E32</f>
-        <v>176.5</v>
+        <v>175</v>
       </c>
       <c r="E33" s="2">
-        <f t="shared" si="1"/>
         <v>186</v>
       </c>
       <c r="F33" s="2">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="34" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A34" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="C34" s="2">
-        <v>160</v>
-      </c>
-      <c r="D34" s="2">
-        <v>168</v>
-      </c>
-      <c r="E34" s="2">
-        <v>178</v>
-      </c>
-      <c r="F34" s="2">
-        <v>186</v>
-      </c>
+        <v>194</v>
+      </c>
+    </row>
+    <row r="34" spans="1:12" ht="22" x14ac:dyDescent="0.3">
+      <c r="C34" s="9" t="s">
+        <v>84</v>
+      </c>
+      <c r="D34" s="7" t="s">
+        <v>95</v>
+      </c>
+      <c r="E34" s="7" t="s">
+        <v>96</v>
+      </c>
+      <c r="F34" s="7" t="s">
+        <v>97</v>
+      </c>
+      <c r="L34" s="1"/>
     </row>
     <row r="35" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A35" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="C35" s="2">
-        <v>168</v>
-      </c>
-      <c r="D35" s="2">
-        <v>175</v>
-      </c>
-      <c r="E35" s="2">
-        <v>186</v>
-      </c>
-      <c r="F35" s="2">
-        <v>194</v>
-      </c>
-    </row>
-    <row r="36" spans="1:12" ht="22" x14ac:dyDescent="0.3">
-      <c r="C36" s="9" t="s">
-        <v>86</v>
-      </c>
-      <c r="D36" s="7" t="s">
-        <v>97</v>
-      </c>
-      <c r="E36" s="7" t="s">
-        <v>98</v>
-      </c>
-      <c r="F36" s="7" t="s">
-        <v>99</v>
-      </c>
-      <c r="L36" s="1"/>
+        <v>31</v>
+      </c>
+      <c r="B35" s="2" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="36" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A36" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="B36" s="2" t="s">
+        <v>69</v>
+      </c>
     </row>
     <row r="37" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A37" s="2" t="s">
-        <v>31</v>
+        <v>70</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>32</v>
+        <v>71</v>
       </c>
     </row>
     <row r="38" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A38" s="2" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
     </row>
     <row r="39" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A39" s="2" t="s">
-        <v>70</v>
+        <v>33</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>71</v>
+        <v>81</v>
       </c>
     </row>
     <row r="40" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A40" s="2" t="s">
-        <v>72</v>
+        <v>34</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
     </row>
     <row r="41" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A41" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="B41" s="2" t="s">
-        <v>83</v>
+        <v>35</v>
       </c>
     </row>
     <row r="42" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A42" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="B42" s="2" t="s">
-        <v>74</v>
+        <v>36</v>
+      </c>
+      <c r="B42" s="2">
+        <v>55</v>
       </c>
     </row>
     <row r="43" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A43" s="2" t="s">
-        <v>35</v>
+        <v>37</v>
+      </c>
+      <c r="B43" s="2">
+        <v>2.2999999999999998</v>
       </c>
     </row>
     <row r="44" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A44" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="B44" s="2">
-        <v>55</v>
+        <v>38</v>
       </c>
     </row>
     <row r="45" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A45" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="B45" s="2">
-        <v>2.2999999999999998</v>
+        <v>39</v>
       </c>
     </row>
     <row r="46" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A46" s="2" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
     </row>
     <row r="47" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A47" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
     </row>
     <row r="48" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A48" s="2" t="s">
-        <v>40</v>
+        <v>42</v>
+      </c>
+      <c r="B48" s="2">
+        <v>142</v>
       </c>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A49" s="2" t="s">
-        <v>41</v>
+        <v>43</v>
+      </c>
+      <c r="B49" s="2">
+        <v>100</v>
       </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A50" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="B50" s="2">
-        <v>142</v>
+        <v>44</v>
+      </c>
+      <c r="B50" s="2" t="s">
+        <v>75</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A51" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="B51" s="2">
-        <v>100</v>
+        <v>45</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A52" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="B52" s="2" t="s">
-        <v>75</v>
+        <v>46</v>
+      </c>
+      <c r="B52" s="2">
+        <v>27.2</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A53" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
+      </c>
+      <c r="B53" s="2" t="s">
+        <v>74</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A54" s="2" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="B54" s="2">
-        <v>27.2</v>
+        <v>44</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A55" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>74</v>
+        <v>105</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A56" s="2" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="B56" s="2">
-        <v>44</v>
+        <v>160</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A57" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="B57" s="2" t="s">
-        <v>107</v>
+        <v>51</v>
+      </c>
+      <c r="B57" s="2">
+        <v>160</v>
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A58" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="B58" s="2">
-        <v>160</v>
+        <v>52</v>
       </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A59" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="B59" s="2">
-        <v>160</v>
+        <v>53</v>
+      </c>
+      <c r="B59" s="2" t="s">
+        <v>82</v>
       </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A60" s="2" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A61" s="2" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>84</v>
+        <v>106</v>
       </c>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A62" s="2" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A63" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="B63" s="2" t="s">
-        <v>108</v>
+        <v>57</v>
       </c>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A64" s="2" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A65" s="2" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A66" s="2" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A67" s="2" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A68" s="2" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
     </row>
     <row r="69" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A69" s="2" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
     </row>
     <row r="70" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A70" s="2" t="s">
-        <v>62</v>
+        <v>64</v>
+      </c>
+      <c r="B70" s="2">
+        <v>1400</v>
       </c>
     </row>
     <row r="71" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A71" s="2" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
     </row>
     <row r="72" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A72" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="B72" s="2">
-        <v>1400</v>
+        <v>66</v>
       </c>
     </row>
     <row r="73" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A73" s="2" t="s">
-        <v>65</v>
+        <v>67</v>
+      </c>
+      <c r="B73" s="2" t="s">
+        <v>111</v>
       </c>
     </row>
     <row r="74" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A74" s="2" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="75" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A75" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="B75" s="2" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="76" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A76" s="2" t="s">
-        <v>112</v>
-      </c>
-      <c r="B76" s="2" t="s">
-        <v>113</v>
+        <v>109</v>
+      </c>
+      <c r="B74" s="2" t="s">
+        <v>110</v>
       </c>
     </row>
   </sheetData>

--- a/data/gravel/Singular Peregrine 2025.xlsx
+++ b/data/gravel/Singular Peregrine 2025.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11018"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3AD870D0-533E-2641-BD13-7CD00CD266E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5293568C-470C-AF4A-9BCF-B88F189C7E0D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="113">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="123" uniqueCount="119">
   <si>
     <t>brand</t>
   </si>
@@ -372,6 +372,24 @@
   </si>
   <si>
     <t>a8:f33</t>
+  </si>
+  <si>
+    <t>head_tube_d</t>
+  </si>
+  <si>
+    <t>headset_upper</t>
+  </si>
+  <si>
+    <t>headset_lower</t>
+  </si>
+  <si>
+    <t>fork_steerer</t>
+  </si>
+  <si>
+    <t>fork_steerer_d</t>
+  </si>
+  <si>
+    <t>fork_material</t>
   </si>
 </sst>
 </file>
@@ -760,7 +778,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:V74"/>
+  <dimension ref="A1:V80"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="20" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="19.6640625" style="2" customWidth="1"/>
@@ -1684,162 +1702,192 @@
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A50" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="B50" s="2" t="s">
-        <v>75</v>
+        <v>113</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A51" s="2" t="s">
-        <v>45</v>
+        <v>114</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A52" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="B52" s="2">
-        <v>27.2</v>
+        <v>115</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A53" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="B53" s="2" t="s">
-        <v>74</v>
+        <v>116</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A54" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="B54" s="2">
-        <v>44</v>
+        <v>117</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A55" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="B55" s="2" t="s">
-        <v>105</v>
+        <v>118</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A56" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="B56" s="2">
-        <v>160</v>
+        <v>44</v>
+      </c>
+      <c r="B56" s="2" t="s">
+        <v>75</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A57" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="B57" s="2">
-        <v>160</v>
+        <v>45</v>
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A58" s="2" t="s">
-        <v>52</v>
+        <v>46</v>
+      </c>
+      <c r="B58" s="2">
+        <v>27.2</v>
       </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A59" s="2" t="s">
-        <v>53</v>
+        <v>47</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>82</v>
+        <v>74</v>
       </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A60" s="2" t="s">
-        <v>54</v>
+        <v>48</v>
+      </c>
+      <c r="B60" s="2">
+        <v>44</v>
       </c>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A61" s="2" t="s">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A62" s="2" t="s">
-        <v>56</v>
+        <v>50</v>
+      </c>
+      <c r="B62" s="2">
+        <v>160</v>
       </c>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A63" s="2" t="s">
-        <v>57</v>
+        <v>51</v>
+      </c>
+      <c r="B63" s="2">
+        <v>160</v>
       </c>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A64" s="2" t="s">
-        <v>58</v>
+        <v>52</v>
       </c>
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A65" s="2" t="s">
-        <v>59</v>
+        <v>53</v>
+      </c>
+      <c r="B65" s="2" t="s">
+        <v>82</v>
       </c>
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A66" s="2" t="s">
-        <v>60</v>
+        <v>54</v>
       </c>
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A67" s="2" t="s">
-        <v>61</v>
+        <v>55</v>
+      </c>
+      <c r="B67" s="2" t="s">
+        <v>106</v>
       </c>
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A68" s="2" t="s">
-        <v>62</v>
+        <v>56</v>
       </c>
     </row>
     <row r="69" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A69" s="2" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
     </row>
     <row r="70" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A70" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="B70" s="2">
-        <v>1400</v>
+        <v>58</v>
       </c>
     </row>
     <row r="71" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A71" s="2" t="s">
-        <v>65</v>
+        <v>59</v>
       </c>
     </row>
     <row r="72" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A72" s="2" t="s">
-        <v>66</v>
+        <v>60</v>
       </c>
     </row>
     <row r="73" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A73" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="B73" s="2" t="s">
-        <v>111</v>
+        <v>61</v>
       </c>
     </row>
     <row r="74" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A74" s="2" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="75" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A75" s="2" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="76" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A76" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="B76" s="2">
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="77" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A77" s="2" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="78" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A78" s="2" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="79" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A79" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="B79" s="2" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="80" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A80" s="2" t="s">
         <v>109</v>
       </c>
-      <c r="B74" s="2" t="s">
+      <c r="B80" s="2" t="s">
         <v>110</v>
       </c>
     </row>
